--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65727D29-2791-493A-882C-15AC382996EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3DF4DE-7671-4E82-B059-9BB5AB1148F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -667,8 +667,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" customWidth="1"/>
-    <col min="3" max="3" width="140.88671875" customWidth="1"/>
+    <col min="2" max="2" width="64.109375" customWidth="1"/>
+    <col min="3" max="3" width="162.109375" customWidth="1"/>
     <col min="4" max="4" width="41.33203125" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="7" max="7" width="21.44140625" customWidth="1"/>
@@ -711,7 +711,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3DF4DE-7671-4E82-B059-9BB5AB1148F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8B9270-1997-444C-8D0B-E04AB1A9DF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -359,7 +359,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +382,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -412,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,6 +447,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -837,69 +850,69 @@
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+    </row>
+    <row r="7" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
     </row>
     <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8B9270-1997-444C-8D0B-E04AB1A9DF94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE90685-9851-47D4-8A48-1FDED54CCD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -454,6 +454,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -914,37 +917,37 @@
       <c r="Y7" s="11"/>
       <c r="Z7" s="11"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
     </row>
     <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
@@ -978,197 +981,197 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+    </row>
+    <row r="11" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+    </row>
+    <row r="12" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+    </row>
+    <row r="13" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+    </row>
+    <row r="14" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+    </row>
+    <row r="15" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
     </row>
     <row r="16" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE90685-9851-47D4-8A48-1FDED54CCD01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED620A61-D369-48E7-BE29-C6DD11C41BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -1587,37 +1587,37 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8" t="s">
+    <row r="29" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
     </row>
     <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED620A61-D369-48E7-BE29-C6DD11C41BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8ED83F-E024-4EB0-9D5E-C35CE1C51C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
   <si>
     <t>Actor</t>
   </si>
@@ -315,6 +315,93 @@
   <si>
     <t>Seccion en la cual, se va a poder volver a imprimir un ticket de compra en el dado caso que haya habido un extravio previo</t>
   </si>
+  <si>
+    <t>Faltantes</t>
+  </si>
+  <si>
+    <t>Formulario Producto</t>
+  </si>
+  <si>
+    <t>Modificar en precio compra para que al darle clic al teclado, se borre ese 0 por default. Hacer que la cantidades ingresadas solo puedan ser valores enteros, para nada aceptar decimales</t>
+  </si>
+  <si>
+    <t>Agregar filtro para consultar los productos de las otras sucursales</t>
+  </si>
+  <si>
+    <t>Actualizar datos de producto</t>
+  </si>
+  <si>
+    <t>Eliminar producto</t>
+  </si>
+  <si>
+    <t>Agregar un menu de confirmacion para hacer esta eliminacion de producto, al igual que una nota del por que se va a eliminar y que se vea reflejado ese movimiento en el historial de movimientos.</t>
+  </si>
+  <si>
+    <t>Salidas y mermas</t>
+  </si>
+  <si>
+    <t>cambiar el combo box de productos por un buscador implementando el mismo metodo para hacer la busqueda</t>
+  </si>
+  <si>
+    <t>Acomodar la seccion de areas que abastece, que mejor sea un buscador y que se vayan agregando las areas si son seleccionadas</t>
+  </si>
+  <si>
+    <t>Paquetes</t>
+  </si>
+  <si>
+    <t>En el recibo establecer que se compro el paquete y no los productos individualmente y al querer hacer la devolucion que se regrese todo el paquete y no un solo producto</t>
+  </si>
+  <si>
+    <t>Todos los archivos</t>
+  </si>
+  <si>
+    <t>para cada seccion en la que se necesita agregar una cantidad y haya un 0, poner ese 0 solo de fondo para que al seleccionar el text box, no tener que borrar ese 0 que ya esta ahi por default</t>
+  </si>
+  <si>
+    <t>Nueva venta</t>
+  </si>
+  <si>
+    <t>poner por defualt el porcentaje de 4.6%</t>
+  </si>
+  <si>
+    <t>Transferencia</t>
+  </si>
+  <si>
+    <t>Generar una nota al momento de aceptar la transferncia para mandarla a la sucursal que va a recibir el pedido</t>
+  </si>
+  <si>
+    <t>Devolucion</t>
+  </si>
+  <si>
+    <t>Poder cancelar una devolucion ya registrada y agregar una nota del porque</t>
+  </si>
+  <si>
+    <t>Seleccionar metodo de pago</t>
+  </si>
+  <si>
+    <t>En transferencia brindar la informacion para agregar la referencia bancaria  y que se guarde en la base de datos, agregar la opcion de pago por transferencia y agregar en pantalla que la informacion del banco de la empresa para completar esa transferencia al igual que nuevamente la parte de la referencia</t>
+  </si>
+  <si>
+    <t>Cliente en una venta</t>
+  </si>
+  <si>
+    <t>Agregar la opcion de dejarle el decuento que le pertenece al cliente o la opcion de quitarle ese descuento y modificarlo con el limite del porcentaje dependiendo del descuento del cliente</t>
+  </si>
+  <si>
+    <t>Al hacer una devolucion, modificar los datos en historial ventas ya que no coincide con la actualizacion</t>
+  </si>
+  <si>
+    <t>Ventas Pendientes</t>
+  </si>
+  <si>
+    <t>Generar un ticket de compra y que se registre en el historial de ventas ya que cuneta como una venta. Actualizar el combo de busqueda de productos y poner un buscador, poner mas detalles en ese formulario</t>
+  </si>
+  <si>
+    <t>Creditos de clientes</t>
+  </si>
+  <si>
+    <t>Agregar los detalles en los que se encuentren que productos saco a credito para ir liquidando los de la fecha mas antigua</t>
+  </si>
 </sst>
 </file>
 
@@ -359,7 +446,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,8 +477,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3939"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -414,11 +519,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -455,6 +575,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -683,7 +819,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
-    <col min="2" max="2" width="64.109375" customWidth="1"/>
+    <col min="2" max="2" width="93.6640625" customWidth="1"/>
     <col min="3" max="3" width="162.109375" customWidth="1"/>
     <col min="4" max="4" width="41.33203125" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
@@ -1203,453 +1339,453 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8" t="s">
+    <row r="17" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8" t="s">
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+    </row>
+    <row r="18" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+    </row>
+    <row r="19" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8" t="s">
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15"/>
+    </row>
+    <row r="20" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8" t="s">
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+    </row>
+    <row r="21" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8" t="s">
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+    </row>
+    <row r="22" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8" t="s">
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+    </row>
+    <row r="23" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8" t="s">
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+    </row>
+    <row r="24" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-    </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8" t="s">
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+    </row>
+    <row r="25" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-    </row>
-    <row r="26" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8" t="s">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+    </row>
+    <row r="26" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8" t="s">
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
+    </row>
+    <row r="27" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-    </row>
-    <row r="28" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8" t="s">
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
+    </row>
+    <row r="28" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10" t="s">
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="15"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="15"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="15"/>
+      <c r="Y28" s="15"/>
+      <c r="Z28" s="15"/>
+    </row>
+    <row r="29" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="11"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="11"/>
-      <c r="Z29" s="11"/>
-    </row>
-    <row r="30" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8" t="s">
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="15"/>
+    </row>
+    <row r="30" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
     </row>
     <row r="31" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1681,37 +1817,37 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9" t="s">
+    <row r="32" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
     </row>
     <row r="33" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
@@ -1745,325 +1881,325 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9" t="s">
+    <row r="34" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-    </row>
-    <row r="35" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9" t="s">
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+    </row>
+    <row r="35" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-    </row>
-    <row r="36" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9" t="s">
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+    </row>
+    <row r="36" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-    </row>
-    <row r="37" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9" t="s">
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+      <c r="Z36" s="15"/>
+    </row>
+    <row r="37" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-    </row>
-    <row r="38" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9" t="s">
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+      <c r="Z37" s="15"/>
+    </row>
+    <row r="38" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="13"/>
+      <c r="B38" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-    </row>
-    <row r="39" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9" t="s">
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+    </row>
+    <row r="39" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="13"/>
+      <c r="B39" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9" t="s">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="11"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11"/>
+      <c r="S39" s="11"/>
+      <c r="T39" s="11"/>
+      <c r="U39" s="11"/>
+      <c r="V39" s="11"/>
+      <c r="W39" s="11"/>
+      <c r="X39" s="11"/>
+      <c r="Y39" s="11"/>
+      <c r="Z39" s="11"/>
+    </row>
+    <row r="40" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9" t="s">
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="15"/>
+      <c r="R40" s="15"/>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="15"/>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
+      <c r="Y40" s="15"/>
+      <c r="Z40" s="15"/>
+    </row>
+    <row r="41" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-    </row>
-    <row r="42" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9" t="s">
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="15"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="15"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
+      <c r="Y41" s="15"/>
+      <c r="Z41" s="15"/>
+    </row>
+    <row r="42" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-    </row>
-    <row r="43" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9" t="s">
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
+      <c r="Y42" s="15"/>
+      <c r="Z42" s="15"/>
+    </row>
+    <row r="43" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11"/>
+      <c r="S43" s="11"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="11"/>
+      <c r="V43" s="11"/>
+      <c r="W43" s="11"/>
+      <c r="X43" s="11"/>
+      <c r="Y43" s="11"/>
+      <c r="Z43" s="11"/>
     </row>
     <row r="44" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
@@ -2097,133 +2233,133 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9" t="s">
+    <row r="45" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-    </row>
-    <row r="46" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9" t="s">
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+      <c r="R45" s="11"/>
+      <c r="S45" s="11"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="11"/>
+      <c r="V45" s="11"/>
+      <c r="W45" s="11"/>
+      <c r="X45" s="11"/>
+      <c r="Y45" s="11"/>
+      <c r="Z45" s="11"/>
+    </row>
+    <row r="46" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-    </row>
-    <row r="47" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9" t="s">
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+      <c r="Q46" s="11"/>
+      <c r="R46" s="11"/>
+      <c r="S46" s="11"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="11"/>
+      <c r="V46" s="11"/>
+      <c r="W46" s="11"/>
+      <c r="X46" s="11"/>
+      <c r="Y46" s="11"/>
+      <c r="Z46" s="11"/>
+    </row>
+    <row r="47" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-    </row>
-    <row r="48" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9" t="s">
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="R47" s="15"/>
+      <c r="S47" s="15"/>
+      <c r="T47" s="15"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="15"/>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
+      <c r="Y47" s="15"/>
+      <c r="Z47" s="15"/>
+    </row>
+    <row r="48" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="11"/>
+      <c r="O48" s="11"/>
+      <c r="P48" s="11"/>
+      <c r="Q48" s="11"/>
+      <c r="R48" s="11"/>
+      <c r="S48" s="11"/>
+      <c r="T48" s="11"/>
+      <c r="U48" s="11"/>
+      <c r="V48" s="11"/>
+      <c r="W48" s="11"/>
+      <c r="X48" s="11"/>
+      <c r="Y48" s="11"/>
+      <c r="Z48" s="11"/>
     </row>
     <row r="49" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
@@ -2257,37 +2393,37 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3" t="s">
+    <row r="50" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
+      <c r="U50" s="11"/>
+      <c r="V50" s="11"/>
+      <c r="W50" s="11"/>
+      <c r="X50" s="11"/>
+      <c r="Y50" s="11"/>
+      <c r="Z50" s="11"/>
     </row>
     <row r="51" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
@@ -2346,9 +2482,10 @@
       <c r="Z52" s="3"/>
     </row>
     <row r="53" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
+      <c r="B53" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="18"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2374,9 +2511,12 @@
       <c r="Z53" s="3"/>
     </row>
     <row r="54" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
+      <c r="B54" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -2402,9 +2542,12 @@
       <c r="Z54" s="3"/>
     </row>
     <row r="55" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
+      <c r="B55" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -2430,9 +2573,12 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="B56" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -2458,9 +2604,12 @@
       <c r="Z56" s="3"/>
     </row>
     <row r="57" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
+      <c r="B57" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>104</v>
+      </c>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2486,9 +2635,12 @@
       <c r="Z57" s="3"/>
     </row>
     <row r="58" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="B58" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>106</v>
+      </c>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -2514,9 +2666,12 @@
       <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
+      <c r="B59" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>107</v>
+      </c>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -2542,9 +2697,12 @@
       <c r="Z59" s="3"/>
     </row>
     <row r="60" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
+      <c r="B60" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2570,9 +2728,12 @@
       <c r="Z60" s="3"/>
     </row>
     <row r="61" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
+      <c r="B61" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>111</v>
+      </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -2598,9 +2759,12 @@
       <c r="Z61" s="3"/>
     </row>
     <row r="62" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
+      <c r="B62" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>113</v>
+      </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -2626,9 +2790,12 @@
       <c r="Z62" s="3"/>
     </row>
     <row r="63" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
+      <c r="B63" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>115</v>
+      </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -2654,9 +2821,12 @@
       <c r="Z63" s="3"/>
     </row>
     <row r="64" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="B64" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>117</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -2682,9 +2852,12 @@
       <c r="Z64" s="3"/>
     </row>
     <row r="65" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
+      <c r="B65" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>119</v>
+      </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -2710,9 +2883,12 @@
       <c r="Z65" s="3"/>
     </row>
     <row r="66" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
+      <c r="B66" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>121</v>
+      </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -2738,9 +2914,12 @@
       <c r="Z66" s="3"/>
     </row>
     <row r="67" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="B67" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>122</v>
+      </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -2766,9 +2945,12 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
+      <c r="B68" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -2794,9 +2976,12 @@
       <c r="Z68" s="3"/>
     </row>
     <row r="69" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
+      <c r="B69" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A8ED83F-E024-4EB0-9D5E-C35CE1C51C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656DB280-26C5-40EB-B7FC-E558EEDF5111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="130">
   <si>
     <t>Actor</t>
   </si>
@@ -402,6 +402,15 @@
   <si>
     <t>Agregar los detalles en los que se encuentren que productos saco a credito para ir liquidando los de la fecha mas antigua</t>
   </si>
+  <si>
+    <t>Hacer que al momento de seleccionar el tipo de venta suelto, habilitar los decimales en la cantidad inicial, stock minimo y maximo. Agregar una caja de texto en la que se le va a agregar un porcentaje de ganancia en la que se va a poder modificar y al modificarla, se va a actualizar el precio dependiendo de ese porcentaje</t>
+  </si>
+  <si>
+    <t>No me funciona el boton de eliminar</t>
+  </si>
+  <si>
+    <t>Hacer que solo se pueda devolver la cantidad que se compro, no de mas</t>
+  </si>
 </sst>
 </file>
 
@@ -446,7 +455,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,6 +504,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -538,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -591,6 +606,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2542,10 +2563,10 @@
       <c r="Z54" s="3"/>
     </row>
     <row r="55" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="20" t="s">
         <v>101</v>
       </c>
       <c r="D55" s="3"/>
@@ -2573,10 +2594,10 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="20" t="s">
         <v>100</v>
       </c>
       <c r="D56" s="3"/>
@@ -2610,7 +2631,9 @@
       <c r="C57" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2703,7 +2726,9 @@
       <c r="C60" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -3008,8 +3033,12 @@
     </row>
     <row r="70" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
+      <c r="B70" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>127</v>
+      </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656DB280-26C5-40EB-B7FC-E558EEDF5111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803F3997-5372-47EC-A9F6-113E3B644A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
   <si>
     <t>Actor</t>
   </si>
@@ -410,6 +410,9 @@
   </si>
   <si>
     <t>Hacer que solo se pueda devolver la cantidad que se compro, no de mas</t>
+  </si>
+  <si>
+    <t>Agregar una seccion de imprimir la nota para mandarla a la otra sucursal y agregar un campo en trnasferencias en el que se pueda ver ese ticket para imprimirlo, al igual que meter un filtro por dias</t>
   </si>
 </sst>
 </file>
@@ -842,7 +845,7 @@
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="2" width="93.6640625" customWidth="1"/>
     <col min="3" max="3" width="162.109375" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" customWidth="1"/>
+    <col min="4" max="4" width="55.44140625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="7" max="7" width="21.44140625" customWidth="1"/>
     <col min="8" max="8" width="41.88671875" customWidth="1"/>
@@ -2784,10 +2787,10 @@
       <c r="Z61" s="3"/>
     </row>
     <row r="62" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="20" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="3"/>
@@ -2821,7 +2824,9 @@
       <c r="C63" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803F3997-5372-47EC-A9F6-113E3B644A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ED9721-97BE-4606-9BC9-62678D4C530C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="148">
   <si>
     <t>Actor</t>
   </si>
@@ -385,12 +385,6 @@
     <t>Cliente en una venta</t>
   </si>
   <si>
-    <t>Agregar la opcion de dejarle el decuento que le pertenece al cliente o la opcion de quitarle ese descuento y modificarlo con el limite del porcentaje dependiendo del descuento del cliente</t>
-  </si>
-  <si>
-    <t>Al hacer una devolucion, modificar los datos en historial ventas ya que no coincide con la actualizacion</t>
-  </si>
-  <si>
     <t>Ventas Pendientes</t>
   </si>
   <si>
@@ -413,6 +407,63 @@
   </si>
   <si>
     <t>Agregar una seccion de imprimir la nota para mandarla a la otra sucursal y agregar un campo en trnasferencias en el que se pueda ver ese ticket para imprimirlo, al igual que meter un filtro por dias</t>
+  </si>
+  <si>
+    <t>No funciona la parte de cancelar, y que se cancelce solo si aun no han pasado las 24 horas de la compra</t>
+  </si>
+  <si>
+    <t>cajeroInventario/nuevaVenta.php</t>
+  </si>
+  <si>
+    <t>Al hacer una devolucion, ingresas el numero de folio y si en cantidad, se compraron 2 productos, y regresas 1, al momento de aceptar la devolucion y volver a buscar ese folio, aun aparece que son 2 productos cuando en realidad ya seria 1. Al igual que en el historial de ventas, si esa compra fue de 1000, al regresar el producto, no se actualiza el valor, ahi tendria que quedar en 500 ya, en vez de los 100</t>
+  </si>
+  <si>
+    <t>cajeroInventario/devoluciones.php y cajeroInventario/historialVentas.php</t>
+  </si>
+  <si>
+    <t>Acomodar el formulario y solo poner una barra de busqueda de los productos y quitar el combo box de los productos, tambien, acomodar el ticket de compra ya que el folio ya no coincide con los demas</t>
+  </si>
+  <si>
+    <t>cajeroInventario/historialVentas.php y cajeroInventario/ventasPendientes.php</t>
+  </si>
+  <si>
+    <t>Agregar una pantalla de confirmacion al momento de darle clic al boton de eliminar producto, al igual que una nota del por que se va a eliminar y que se vea reflejado ese movimiento en el historial de movimientos.</t>
+  </si>
+  <si>
+    <t>cajeroInventario/productos.php y cajeroInventario/historial.php</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>quitar el combo box de productos y hacer que el buscador de productos me funcione ya que no me carga ningun producto</t>
+  </si>
+  <si>
+    <t>cajeroInventario/salidas.php</t>
+  </si>
+  <si>
+    <t>Acomodar la seccion de areas que abastece, en vez de que este ese combo box, que sea un buscador normal en el que se le pueda estar agregando varias areas</t>
+  </si>
+  <si>
+    <t>cajeroInventario/proveedores.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se pueden regresar mas productos de las que fueron compradas </t>
+  </si>
+  <si>
+    <t>si le quiero hacer un backspace al porcentaje de descuento del cliente, no me deja</t>
+  </si>
+  <si>
+    <t>cajeroInventario/devoluciones.php</t>
+  </si>
+  <si>
+    <t>Ruta</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
   </si>
 </sst>
 </file>
@@ -458,7 +509,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,6 +564,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -556,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -615,6 +672,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2535,10 +2598,10 @@
       <c r="Z53" s="3"/>
     </row>
     <row r="54" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="20" t="s">
         <v>100</v>
       </c>
       <c r="D54" s="3"/>
@@ -2628,6 +2691,9 @@
       <c r="Z56" s="3"/>
     </row>
     <row r="57" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>137</v>
+      </c>
       <c r="B57" s="19" t="s">
         <v>103</v>
       </c>
@@ -2635,7 +2701,7 @@
         <v>104</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2661,6 +2727,9 @@
       <c r="Z57" s="3"/>
     </row>
     <row r="58" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>137</v>
+      </c>
       <c r="B58" s="19" t="s">
         <v>105</v>
       </c>
@@ -2730,7 +2799,7 @@
         <v>109</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2825,7 +2894,7 @@
         <v>115</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -2857,7 +2926,9 @@
       <c r="C64" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -2913,13 +2984,6 @@
       <c r="Z65" s="3"/>
     </row>
     <row r="66" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B66" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -2944,12 +3008,8 @@
       <c r="Z66" s="3"/>
     </row>
     <row r="67" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B67" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>122</v>
-      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -2976,10 +3036,10 @@
     </row>
     <row r="68" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B68" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3007,10 +3067,10 @@
     </row>
     <row r="69" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B69" s="19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3042,7 +3102,7 @@
         <v>99</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -3069,9 +3129,6 @@
       <c r="Z70" s="3"/>
     </row>
     <row r="71" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -3097,9 +3154,15 @@
       <c r="Z71" s="3"/>
     </row>
     <row r="72" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
+      <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>147</v>
+      </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -3125,9 +3188,15 @@
       <c r="Z72" s="3"/>
     </row>
     <row r="73" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
+      <c r="A73" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -3153,9 +3222,15 @@
       <c r="Z73" s="3"/>
     </row>
     <row r="74" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
+      <c r="A74" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -3181,9 +3256,15 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="3"/>
+      <c r="A75" t="s">
+        <v>130</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>143</v>
+      </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -3209,9 +3290,15 @@
       <c r="Z75" s="3"/>
     </row>
     <row r="76" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
+      <c r="A76" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>135</v>
+      </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -3237,9 +3324,15 @@
       <c r="Z76" s="3"/>
     </row>
     <row r="77" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
+      <c r="A77" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C77" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -3265,9 +3358,15 @@
       <c r="Z77" s="3"/>
     </row>
     <row r="78" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
+      <c r="A78" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>140</v>
+      </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -3293,9 +3392,15 @@
       <c r="Z78" s="3"/>
     </row>
     <row r="79" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
+      <c r="A79" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -3322,8 +3427,12 @@
     </row>
     <row r="80" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
+      <c r="B80" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>111</v>
+      </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -3350,9 +3459,15 @@
     </row>
     <row r="81" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
+      <c r="B81" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -3378,9 +3493,15 @@
     </row>
     <row r="82" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
+      <c r="B82" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -3406,8 +3527,12 @@
     </row>
     <row r="83" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
+      <c r="B83" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>119</v>
+      </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -3434,9 +3559,8 @@
     </row>
     <row r="84" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -3462,8 +3586,12 @@
     </row>
     <row r="85" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
+      <c r="B85" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>122</v>
+      </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -3490,8 +3618,12 @@
     </row>
     <row r="86" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
+      <c r="B86" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -3518,8 +3650,6 @@
     </row>
     <row r="87" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -677,7 +677,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ED9721-97BE-4606-9BC9-62678D4C530C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36F4871-6D92-44DB-AA33-35BFED00867F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="147">
   <si>
     <t>Actor</t>
   </si>
@@ -382,9 +383,6 @@
     <t>En transferencia brindar la informacion para agregar la referencia bancaria  y que se guarde en la base de datos, agregar la opcion de pago por transferencia y agregar en pantalla que la informacion del banco de la empresa para completar esa transferencia al igual que nuevamente la parte de la referencia</t>
   </si>
   <si>
-    <t>Cliente en una venta</t>
-  </si>
-  <si>
     <t>Ventas Pendientes</t>
   </si>
   <si>
@@ -410,9 +408,6 @@
   </si>
   <si>
     <t>No funciona la parte de cancelar, y que se cancelce solo si aun no han pasado las 24 horas de la compra</t>
-  </si>
-  <si>
-    <t>cajeroInventario/nuevaVenta.php</t>
   </si>
   <si>
     <t>Al hacer una devolucion, ingresas el numero de folio y si en cantidad, se compraron 2 productos, y regresas 1, al momento de aceptar la devolucion y volver a buscar ese folio, aun aparece que son 2 productos cuando en realidad ya seria 1. Al igual que en el historial de ventas, si esa compra fue de 1000, al regresar el producto, no se actualiza el valor, ahi tendria que quedar en 500 ya, en vez de los 100</t>
@@ -451,9 +446,6 @@
     <t xml:space="preserve">Se pueden regresar mas productos de las que fueron compradas </t>
   </si>
   <si>
-    <t>si le quiero hacer un backspace al porcentaje de descuento del cliente, no me deja</t>
-  </si>
-  <si>
     <t>cajeroInventario/devoluciones.php</t>
   </si>
   <si>
@@ -464,6 +456,12 @@
   </si>
   <si>
     <t>Descripcion</t>
+  </si>
+  <si>
+    <t>El folio lo imprime mal en el ticket, sale el numero de folio con su fecha</t>
+  </si>
+  <si>
+    <t>Problema</t>
   </si>
 </sst>
 </file>
@@ -2692,7 +2690,7 @@
     </row>
     <row r="57" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>103</v>
@@ -2701,7 +2699,7 @@
         <v>104</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2728,7 +2726,7 @@
     </row>
     <row r="58" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>105</v>
@@ -2799,7 +2797,7 @@
         <v>109</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -2894,7 +2892,7 @@
         <v>115</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -2927,7 +2925,7 @@
         <v>117</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3036,10 +3034,10 @@
     </row>
     <row r="68" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B68" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3067,10 +3065,10 @@
     </row>
     <row r="69" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B69" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3102,7 +3100,7 @@
         <v>99</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -3155,13 +3153,13 @@
     </row>
     <row r="72" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -3189,13 +3187,13 @@
     </row>
     <row r="73" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -3223,13 +3221,13 @@
     </row>
     <row r="74" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -3256,15 +3254,8 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>130</v>
-      </c>
-      <c r="B75" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>143</v>
-      </c>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -3291,13 +3282,13 @@
     </row>
     <row r="76" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B76" s="22" t="s">
         <v>103</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3325,13 +3316,13 @@
     </row>
     <row r="77" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B77" s="22" t="s">
         <v>105</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3359,13 +3350,13 @@
     </row>
     <row r="78" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B78" s="22" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3393,13 +3384,13 @@
     </row>
     <row r="79" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B79" s="22" t="s">
         <v>116</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3466,7 +3457,7 @@
         <v>115</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -3500,7 +3491,7 @@
         <v>117</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -3587,10 +3578,10 @@
     <row r="85" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -3619,10 +3610,10 @@
     <row r="86" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -3704,8 +3695,12 @@
     </row>
     <row r="89" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
+      <c r="B89" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -29605,4 +29600,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046017EA-D8E7-4757-AD1B-1B80A3D154B6}">
+  <dimension ref="B1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="32.21875" customWidth="1"/>
+    <col min="3" max="3" width="70.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36F4871-6D92-44DB-AA33-35BFED00867F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB83C5D-0AED-4166-AB0B-B468B47A7229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
+    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="149">
   <si>
     <t>Actor</t>
   </si>
@@ -462,6 +463,12 @@
   </si>
   <si>
     <t>Problema</t>
+  </si>
+  <si>
+    <t>Ver que impresora tienen</t>
+  </si>
+  <si>
+    <t>Metodos de pago en ventas pendientes</t>
   </si>
 </sst>
 </file>
@@ -2692,10 +2699,10 @@
       <c r="A57" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="19" t="s">
+      <c r="B57" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="20" t="s">
         <v>104</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -2728,10 +2735,10 @@
       <c r="A58" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="20" t="s">
         <v>106</v>
       </c>
       <c r="D58" s="3"/>
@@ -2759,10 +2766,10 @@
       <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B59" s="19" t="s">
+      <c r="B59" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="20" t="s">
         <v>107</v>
       </c>
       <c r="D59" s="3"/>
@@ -2790,10 +2797,10 @@
       <c r="Z59" s="3"/>
     </row>
     <row r="60" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="20" t="s">
         <v>109</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -2823,10 +2830,10 @@
       <c r="Z60" s="3"/>
     </row>
     <row r="61" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D61" s="3"/>
@@ -3006,8 +3013,8 @@
       <c r="Z66" s="3"/>
     </row>
     <row r="67" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3033,10 +3040,10 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" s="20" t="s">
         <v>121</v>
       </c>
       <c r="D68" s="3"/>
@@ -3223,10 +3230,10 @@
       <c r="A74" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="21" t="s">
         <v>131</v>
       </c>
       <c r="D74" s="3"/>
@@ -3284,10 +3291,10 @@
       <c r="A76" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="22" t="s">
+      <c r="B76" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C76" s="22" t="s">
+      <c r="C76" s="20" t="s">
         <v>133</v>
       </c>
       <c r="D76" s="3"/>
@@ -3318,10 +3325,10 @@
       <c r="A77" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B77" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C77" s="20" t="s">
         <v>136</v>
       </c>
       <c r="D77" s="3"/>
@@ -3352,10 +3359,10 @@
       <c r="A78" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B78" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="22" t="s">
+      <c r="C78" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D78" s="3"/>
@@ -3418,10 +3425,10 @@
     </row>
     <row r="80" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="19" t="s">
+      <c r="B80" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="20" t="s">
         <v>111</v>
       </c>
       <c r="D80" s="3"/>
@@ -29603,6 +29610,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CBDBA7-7558-43E4-AF0C-E78E0F1074DB}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046017EA-D8E7-4757-AD1B-1B80A3D154B6}">
   <dimension ref="B1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB83C5D-0AED-4166-AB0B-B468B47A7229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DB1FB2-AA7E-4C96-983C-EE708F7C1C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
-    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId3"/>
+    <sheet name="Detalles por agregar" sheetId="4" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
+    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="161">
   <si>
     <t>Actor</t>
   </si>
@@ -469,6 +470,42 @@
   </si>
   <si>
     <t>Metodos de pago en ventas pendientes</t>
+  </si>
+  <si>
+    <t>Detalles</t>
+  </si>
+  <si>
+    <t>Agregar la funcion de editar el precio del producto en un dado caso de algun producto dañado, agregar el porcentaje de lo que le estas rebajando y que no exceda el precio de compra</t>
+  </si>
+  <si>
+    <t>Agregar metodo de pago de transferencia en abonos</t>
+  </si>
+  <si>
+    <t>Agregar la unidad de medida</t>
+  </si>
+  <si>
+    <t>En compras a proveedor, agregar funcion de modificar el precio de compra por si llega a subir ese precio y actualizarlo con el precio del inventario</t>
+  </si>
+  <si>
+    <t>Agregar funcion par ala sucursal que envia en trasferencias de editar la cantidad de productos a enviar</t>
+  </si>
+  <si>
+    <t>Agregar una funcion de exportar todos los clientes que deben dinero ya con la cantidad por cobrar</t>
+  </si>
+  <si>
+    <t>Agregar funcionalidad de promociones</t>
+  </si>
+  <si>
+    <t>Agregar una funcion para entradas y salidas de dinero en la caja sin registrar la venta de compra</t>
+  </si>
+  <si>
+    <t>Agregar la funcoin de la caja automatica</t>
+  </si>
+  <si>
+    <t>Agregar la funcion de editar ticket en donde se va a incluir el logo de la sucursal</t>
+  </si>
+  <si>
+    <t>Aregar la funcion para acomodar los tamaños de letra del ticket</t>
   </si>
 </sst>
 </file>
@@ -29610,6 +29647,76 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B42946-3D8D-41E9-B897-1FA35180431E}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CBDBA7-7558-43E4-AF0C-E78E0F1074DB}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -29632,7 +29739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046017EA-D8E7-4757-AD1B-1B80A3D154B6}">
   <dimension ref="B1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DB1FB2-AA7E-4C96-983C-EE708F7C1C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340D6BB5-7441-43F9-934C-7F6F4CD5E4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="160">
   <si>
     <t>Actor</t>
   </si>
@@ -499,9 +499,6 @@
     <t>Agregar una funcion para entradas y salidas de dinero en la caja sin registrar la venta de compra</t>
   </si>
   <si>
-    <t>Agregar la funcoin de la caja automatica</t>
-  </si>
-  <si>
     <t>Agregar la funcion de editar ticket en donde se va a incluir el logo de la sucursal</t>
   </si>
   <si>
@@ -655,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -722,6 +719,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29648,8 +29646,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06B42946-3D8D-41E9-B897-1FA35180431E}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="160.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -29657,7 +29658,7 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="24" t="s">
         <v>150</v>
       </c>
     </row>
@@ -29704,11 +29705,6 @@
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340D6BB5-7441-43F9-934C-7F6F4CD5E4A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006DF406-358A-4937-A85B-63EC1B2C1919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -487,9 +487,6 @@
     <t>En compras a proveedor, agregar funcion de modificar el precio de compra por si llega a subir ese precio y actualizarlo con el precio del inventario</t>
   </si>
   <si>
-    <t>Agregar funcion par ala sucursal que envia en trasferencias de editar la cantidad de productos a enviar</t>
-  </si>
-  <si>
     <t>Agregar una funcion de exportar todos los clientes que deben dinero ya con la cantidad por cobrar</t>
   </si>
   <si>
@@ -503,6 +500,9 @@
   </si>
   <si>
     <t>Aregar la funcion para acomodar los tamaños de letra del ticket</t>
+  </si>
+  <si>
+    <t>Agregar funcion par a la sucursal que envia en trasferencias de editar la cantidad de productos a enviar</t>
   </si>
 </sst>
 </file>
@@ -29663,48 +29663,48 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="24" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="24" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="24" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>158</v>
-      </c>
-    </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,22 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006DF406-358A-4937-A85B-63EC1B2C1919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605DD6AB-46F4-4F78-8FB5-455106327CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
     <sheet name="Detalles por agregar" sheetId="4" r:id="rId2"/>
     <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
-    <sheet name="Detalles Pequeños" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
   <si>
     <t>Actor</t>
   </si>
@@ -463,9 +462,6 @@
     <t>El folio lo imprime mal en el ticket, sale el numero de folio con su fecha</t>
   </si>
   <si>
-    <t>Problema</t>
-  </si>
-  <si>
     <t>Ver que impresora tienen</t>
   </si>
   <si>
@@ -548,7 +544,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,6 +602,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -691,9 +693,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -720,6 +719,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,37 +1468,37 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14" t="s">
+    <row r="17" spans="1:26" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
     </row>
     <row r="18" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
@@ -1530,101 +1532,101 @@
       <c r="Y18" s="11"/>
       <c r="Z18" s="11"/>
     </row>
-    <row r="19" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14" t="s">
+    <row r="19" spans="1:26" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
-    </row>
-    <row r="20" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14" t="s">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+    </row>
+    <row r="20" spans="1:26" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-    </row>
-    <row r="21" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14" t="s">
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+    </row>
+    <row r="21" spans="1:26" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
     </row>
     <row r="22" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
@@ -1658,37 +1660,37 @@
       <c r="Y22" s="11"/>
       <c r="Z22" s="11"/>
     </row>
-    <row r="23" spans="1:26" s="16" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="1:26" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
     </row>
     <row r="24" spans="1:26" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
@@ -1754,37 +1756,37 @@
       <c r="Y25" s="11"/>
       <c r="Z25" s="11"/>
     </row>
-    <row r="26" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14" t="s">
+    <row r="26" spans="1:26" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
     </row>
     <row r="27" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
@@ -1818,69 +1820,69 @@
       <c r="Y27" s="11"/>
       <c r="Z27" s="11"/>
     </row>
-    <row r="28" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14" t="s">
+    <row r="28" spans="1:26" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="S28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-    </row>
-    <row r="29" spans="1:26" s="16" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14" t="s">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+    </row>
+    <row r="29" spans="1:26" s="15" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="S29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
     </row>
     <row r="30" spans="1:26" s="12" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
@@ -2072,69 +2074,69 @@
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
     </row>
-    <row r="36" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17" t="s">
+    <row r="36" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="15"/>
-      <c r="Z36" s="15"/>
-    </row>
-    <row r="37" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17" t="s">
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+    </row>
+    <row r="37" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
     </row>
     <row r="38" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
@@ -2200,101 +2202,101 @@
       <c r="Y39" s="11"/>
       <c r="Z39" s="11"/>
     </row>
-    <row r="40" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17" t="s">
+    <row r="40" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="16"/>
+      <c r="B40" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="15"/>
-      <c r="Z40" s="15"/>
-    </row>
-    <row r="41" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17" t="s">
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="14"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="14"/>
+    </row>
+    <row r="41" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="15"/>
-    </row>
-    <row r="42" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17" t="s">
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+    </row>
+    <row r="42" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="15"/>
-      <c r="W42" s="15"/>
-      <c r="X42" s="15"/>
-      <c r="Y42" s="15"/>
-      <c r="Z42" s="15"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14"/>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
     </row>
     <row r="43" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
@@ -2424,37 +2426,37 @@
       <c r="Y46" s="11"/>
       <c r="Z46" s="11"/>
     </row>
-    <row r="47" spans="1:26" s="16" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17" t="s">
+    <row r="47" spans="1:26" s="15" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
-      <c r="U47" s="15"/>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
-      <c r="Y47" s="15"/>
-      <c r="Z47" s="15"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
     </row>
     <row r="48" spans="1:26" s="12" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
@@ -2609,10 +2611,10 @@
       <c r="Z52" s="3"/>
     </row>
     <row r="53" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="18"/>
+      <c r="C53" s="17"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -2638,10 +2640,10 @@
       <c r="Z53" s="3"/>
     </row>
     <row r="54" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>100</v>
       </c>
       <c r="D54" s="3"/>
@@ -2669,10 +2671,10 @@
       <c r="Z54" s="3"/>
     </row>
     <row r="55" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="19" t="s">
         <v>101</v>
       </c>
       <c r="D55" s="3"/>
@@ -2700,10 +2702,10 @@
       <c r="Z55" s="3"/>
     </row>
     <row r="56" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="19" t="s">
         <v>100</v>
       </c>
       <c r="D56" s="3"/>
@@ -2734,10 +2736,10 @@
       <c r="A57" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="19" t="s">
         <v>104</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -2770,10 +2772,10 @@
       <c r="A58" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="19" t="s">
         <v>106</v>
       </c>
       <c r="D58" s="3"/>
@@ -2801,10 +2803,10 @@
       <c r="Z58" s="3"/>
     </row>
     <row r="59" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="19" t="s">
         <v>107</v>
       </c>
       <c r="D59" s="3"/>
@@ -2832,10 +2834,10 @@
       <c r="Z59" s="3"/>
     </row>
     <row r="60" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="19" t="s">
         <v>109</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -2865,10 +2867,10 @@
       <c r="Z60" s="3"/>
     </row>
     <row r="61" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="19" t="s">
         <v>111</v>
       </c>
       <c r="D61" s="3"/>
@@ -2896,10 +2898,10 @@
       <c r="Z61" s="3"/>
     </row>
     <row r="62" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="19" t="s">
         <v>113</v>
       </c>
       <c r="D62" s="3"/>
@@ -3048,8 +3050,8 @@
       <c r="Z66" s="3"/>
     </row>
     <row r="67" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B67" s="22"/>
-      <c r="C67" s="22"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3075,10 +3077,10 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="19" t="s">
         <v>121</v>
       </c>
       <c r="D68" s="3"/>
@@ -3138,10 +3140,10 @@
     </row>
     <row r="70" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>124</v>
       </c>
       <c r="D70" s="3"/>
@@ -3197,10 +3199,10 @@
       <c r="A72" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="22" t="s">
         <v>144</v>
       </c>
       <c r="D72" s="3"/>
@@ -3265,10 +3267,10 @@
       <c r="A74" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="21" t="s">
+      <c r="C74" s="20" t="s">
         <v>131</v>
       </c>
       <c r="D74" s="3"/>
@@ -3296,8 +3298,8 @@
       <c r="Z74" s="3"/>
     </row>
     <row r="75" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -3326,10 +3328,10 @@
       <c r="A76" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="B76" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="19" t="s">
         <v>133</v>
       </c>
       <c r="D76" s="3"/>
@@ -3360,10 +3362,10 @@
       <c r="A77" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="B77" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="20" t="s">
+      <c r="C77" s="19" t="s">
         <v>136</v>
       </c>
       <c r="D77" s="3"/>
@@ -3394,10 +3396,10 @@
       <c r="A78" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="20" t="s">
+      <c r="C78" s="19" t="s">
         <v>138</v>
       </c>
       <c r="D78" s="3"/>
@@ -3428,7 +3430,7 @@
       <c r="A79" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B79" s="22" t="s">
+      <c r="B79" s="21" t="s">
         <v>116</v>
       </c>
       <c r="C79" s="3" t="s">
@@ -3460,10 +3462,10 @@
     </row>
     <row r="80" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="19" t="s">
         <v>111</v>
       </c>
       <c r="D80" s="3"/>
@@ -3492,10 +3494,10 @@
     </row>
     <row r="81" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="18" t="s">
         <v>115</v>
       </c>
       <c r="D81" s="3" t="s">
@@ -3592,8 +3594,8 @@
     </row>
     <row r="84" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -29654,57 +29656,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>157</v>
-      </c>
-    </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -29722,34 +29724,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{046017EA-D8E7-4757-AD1B-1B80A3D154B6}">
-  <dimension ref="B1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="32.21875" customWidth="1"/>
-    <col min="3" max="3" width="70.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605DD6AB-46F4-4F78-8FB5-455106327CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52631ABC-5608-482D-9668-D3FC855176E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
     <sheet name="Detalles por agregar" sheetId="4" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
+    <sheet name="Pruebas InventarioCajero" sheetId="3" r:id="rId3"/>
+    <sheet name="Pruebas InventarioCajero (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="198">
   <si>
     <t>Actor</t>
   </si>
@@ -462,12 +463,6 @@
     <t>El folio lo imprime mal en el ticket, sale el numero de folio con su fecha</t>
   </si>
   <si>
-    <t>Ver que impresora tienen</t>
-  </si>
-  <si>
-    <t>Metodos de pago en ventas pendientes</t>
-  </si>
-  <si>
     <t>Detalles</t>
   </si>
   <si>
@@ -500,12 +495,135 @@
   <si>
     <t>Agregar funcion par a la sucursal que envia en trasferencias de editar la cantidad de productos a enviar</t>
   </si>
+  <si>
+    <t>Modulo</t>
+  </si>
+  <si>
+    <t>Inicio</t>
+  </si>
+  <si>
+    <t>Nueva Venta</t>
+  </si>
+  <si>
+    <t>Historial Ventas</t>
+  </si>
+  <si>
+    <t>Devoluciones</t>
+  </si>
+  <si>
+    <t>Abrir Caja</t>
+  </si>
+  <si>
+    <t>Corte de Caja</t>
+  </si>
+  <si>
+    <t>Clientes</t>
+  </si>
+  <si>
+    <t>Creditos</t>
+  </si>
+  <si>
+    <t>Productos</t>
+  </si>
+  <si>
+    <t>Categorias</t>
+  </si>
+  <si>
+    <t>Unidades de Medida</t>
+  </si>
+  <si>
+    <t>Entradas</t>
+  </si>
+  <si>
+    <t>Salidas y Mermas</t>
+  </si>
+  <si>
+    <t>Movimientos</t>
+  </si>
+  <si>
+    <t>Proovedores</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Transferencias</t>
+  </si>
+  <si>
+    <t>Promociones</t>
+  </si>
+  <si>
+    <t>Mas Vendidos</t>
+  </si>
+  <si>
+    <t>Funciona?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                              Rol de Inventario\Cajero</t>
+  </si>
+  <si>
+    <t>Usuarios</t>
+  </si>
+  <si>
+    <t>Sucursales</t>
+  </si>
+  <si>
+    <t>Ventas</t>
+  </si>
+  <si>
+    <t>Productos mas Vendidos</t>
+  </si>
+  <si>
+    <t>Historial Movimientos</t>
+  </si>
+  <si>
+    <t>Abonos</t>
+  </si>
+  <si>
+    <t>Inicio Inventario</t>
+  </si>
+  <si>
+    <t>Unidades de medida</t>
+  </si>
+  <si>
+    <t>Salidas</t>
+  </si>
+  <si>
+    <t>Proveedores</t>
+  </si>
+  <si>
+    <t>Mas vendidos</t>
+  </si>
+  <si>
+    <t>Inicio Cajero</t>
+  </si>
+  <si>
+    <t>Historial Cortes</t>
+  </si>
+  <si>
+    <t>Clientes Cajero</t>
+  </si>
+  <si>
+    <t>Venta Pendientes</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                        Rol de Administrador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                    Simulacion a Inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                            Simulacion a Cajero</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -543,8 +661,23 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -611,8 +744,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -650,11 +801,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -722,12 +910,42 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0099FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -29656,57 +29874,57 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>156</v>
-      </c>
-    </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -29716,21 +29934,465 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8CBDBA7-7558-43E4-AF0C-E78E0F1074DB}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="26" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>147</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>158</v>
       </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="27"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A65C766-BE56-42C8-8ED0-B693D28207BC}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="27"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="29"/>
+      <c r="C27" s="30"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52631ABC-5608-482D-9668-D3FC855176E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28500A3-16DA-4618-96BE-EC1C0FEC23E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="198">
   <si>
     <t>Actor</t>
   </si>
@@ -30160,14 +30160,18 @@
       <c r="A4" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="25"/>
+      <c r="B4" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C4" s="25"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C5" s="25"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28500A3-16DA-4618-96BE-EC1C0FEC23E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBAC652-8CE2-4091-AAD7-5C21BE5DBAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="199">
   <si>
     <t>Actor</t>
   </si>
@@ -618,6 +618,9 @@
   <si>
     <t xml:space="preserve">                                                            Simulacion a Cajero</t>
   </si>
+  <si>
+    <t>Solo cambiar lo de la fecha de vencimiento</t>
+  </si>
 </sst>
 </file>
 
@@ -30178,36 +30181,48 @@
       <c r="A6" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B6" s="25"/>
+      <c r="B6" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C6" s="25"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C7" s="25"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C8" s="25"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C9" s="25"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
+      <c r="B10" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBAC652-8CE2-4091-AAD7-5C21BE5DBAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AF10D5-D750-42A9-AB62-9CA7BB712120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
     <sheet name="Detalles por agregar" sheetId="4" r:id="rId2"/>
     <sheet name="Pruebas InventarioCajero" sheetId="3" r:id="rId3"/>
-    <sheet name="Pruebas InventarioCajero (2)" sheetId="5" r:id="rId4"/>
+    <sheet name="Pruebas Adminsistrador" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21AF10D5-D750-42A9-AB62-9CA7BB712120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FBC41D-AE5D-428D-BF83-41E4EB42679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="199">
   <si>
     <t>Actor</t>
   </si>
@@ -29967,14 +29967,18 @@
       <c r="A3" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="B3" s="32"/>
+      <c r="B3" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C3" s="27"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="27"/>
+      <c r="B4" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C4" s="27"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FBC41D-AE5D-428D-BF83-41E4EB42679C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733A5EFB-5330-4B08-AE47-110509F03D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="199">
   <si>
     <t>Actor</t>
   </si>
@@ -29985,7 +29985,9 @@
       <c r="A5" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C5" s="27"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FerreteriaAldrete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733A5EFB-5330-4B08-AE47-110509F03D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F26E83-98A6-4B80-A169-A0F887911750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="199">
   <si>
     <t>Actor</t>
   </si>
@@ -30008,7 +30008,9 @@
       <c r="A8" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C8" s="27"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -30029,7 +30031,9 @@
       <c r="A11" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="32" t="s">
+        <v>194</v>
+      </c>
       <c r="C11" s="27"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">

--- a/Funcionalidades del Sistema Ferreteria.xlsx
+++ b/Funcionalidades del Sistema Ferreteria.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F26E83-98A6-4B80-A169-A0F887911750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Pruebas Adminsistrador" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
